--- a/app/src/main/res/raw/inmigration_form.xlsx
+++ b/app/src/main/res/raw/inmigration_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27795" windowHeight="12195" tabRatio="500"/>
+    <workbookView windowWidth="24090" windowHeight="11400" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="265">
   <si>
     <t>group</t>
   </si>
@@ -818,6 +818,9 @@
   </si>
   <si>
     <t>DONT_KNOW</t>
+  </si>
+  <si>
+    <t>LOADED_EXTERNALLY</t>
   </si>
   <si>
     <t>form_id</t>
@@ -849,12 +852,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -886,6 +889,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial [Mono]"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Arial"/>
@@ -896,20 +912,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -926,7 +928,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -934,6 +936,14 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -961,24 +971,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -994,29 +1003,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1032,6 +1019,28 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1081,13 +1090,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1099,7 +1114,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1117,19 +1144,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1141,61 +1204,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1207,19 +1228,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1237,19 +1246,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1358,15 +1367,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
@@ -1398,21 +1398,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1437,127 +1422,151 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1566,26 +1575,26 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1614,6 +1623,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2058,7 +2071,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="35" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -2076,7 +2089,7 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="48" t="s">
+      <c r="P1" s="50" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -2092,24 +2105,24 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="17" t="s">
         <v>21</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="17" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="1"/>
@@ -2120,7 +2133,7 @@
       <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="48"/>
+      <c r="P2" s="50"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
@@ -2138,14 +2151,14 @@
       <c r="I3" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="34" t="s">
+      <c r="K3" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
       <c r="N3" t="b">
         <v>1</v>
       </c>
@@ -2169,14 +2182,14 @@
       <c r="I4" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
       <c r="N4" t="b">
         <v>1</v>
       </c>
@@ -2201,18 +2214,18 @@
       <c r="I5" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="K5" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
       <c r="N5" t="b">
         <v>1</v>
       </c>
-      <c r="P5" s="49" t="s">
+      <c r="P5" s="51" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2235,14 +2248,14 @@
       <c r="I6" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="34" t="s">
+      <c r="K6" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
       <c r="N6" t="b">
         <v>1</v>
       </c>
@@ -2267,14 +2280,14 @@
       <c r="I7" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="34" t="s">
+      <c r="K7" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
       <c r="N7" t="b">
         <v>1</v>
       </c>
@@ -2296,14 +2309,14 @@
       <c r="I8" t="s">
         <v>59</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="K8" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
       <c r="N8" t="b">
         <v>1</v>
       </c>
@@ -2325,14 +2338,14 @@
       <c r="I9" t="s">
         <v>65</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="34" t="s">
+      <c r="K9" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
       <c r="N9" t="b">
         <v>1</v>
       </c>
@@ -2354,14 +2367,14 @@
       <c r="I10" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="K10" s="34" t="s">
+      <c r="K10" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
       <c r="N10" t="b">
         <v>1</v>
       </c>
@@ -2380,14 +2393,14 @@
       <c r="I11" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="K11" s="34" t="s">
+      <c r="K11" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
       <c r="N11" t="b">
         <v>1</v>
       </c>
@@ -2396,378 +2409,378 @@
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27" t="s">
+      <c r="G12" s="29"/>
+      <c r="H12" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="27" t="s">
+      <c r="I12" s="29" t="s">
         <v>83</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K12" s="36" t="s">
+      <c r="K12" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="27" t="b">
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="29" t="b">
         <v>1</v>
       </c>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27" t="s">
+      <c r="O12" s="29"/>
+      <c r="P12" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="Q12" s="27"/>
+      <c r="Q12" s="29"/>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27" t="s">
+      <c r="G13" s="29"/>
+      <c r="H13" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="I13" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J13" s="38" t="s">
+      <c r="J13" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="K13" s="36" t="s">
+      <c r="K13" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="27" t="b">
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="29" t="b">
         <v>1</v>
       </c>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-    </row>
-    <row r="14" s="22" customFormat="1" spans="1:14">
-      <c r="A14" s="28"/>
-      <c r="D14" s="22" t="s">
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+    </row>
+    <row r="14" s="24" customFormat="1" spans="1:14">
+      <c r="A14" s="30"/>
+      <c r="D14" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="J14" s="39" t="s">
+      <c r="J14" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="K14" s="40" t="s">
+      <c r="K14" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="22" t="b">
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="24" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" s="22" customFormat="1" spans="1:17">
-      <c r="A15" s="28"/>
-      <c r="D15" s="22" t="s">
+    <row r="15" s="24" customFormat="1" spans="1:17">
+      <c r="A15" s="30"/>
+      <c r="D15" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="J15" s="39" t="s">
+      <c r="J15" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="K15" s="40" t="s">
+      <c r="K15" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="22" t="b">
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="P15" s="22" t="s">
+      <c r="P15" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="Q15" s="22" t="s">
+      <c r="Q15" s="24" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="16" s="22" customFormat="1" spans="1:17">
-      <c r="A16" s="28"/>
-      <c r="D16" s="22" t="s">
+    <row r="16" s="24" customFormat="1" spans="1:17">
+      <c r="A16" s="30"/>
+      <c r="D16" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="J16" s="39" t="s">
+      <c r="J16" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="K16" s="40" t="s">
+      <c r="K16" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="P16" s="22" t="s">
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="P16" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="Q16" s="22" t="s">
+      <c r="Q16" s="24" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="17" s="23" customFormat="1" spans="1:15">
-      <c r="A17" s="29" t="s">
+    <row r="17" s="25" customFormat="1" spans="1:15">
+      <c r="A17" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="23" t="s">
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="23" t="s">
+      <c r="I17" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="J17" s="23" t="s">
+      <c r="J17" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="K17" s="42" t="s">
+      <c r="K17" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="23" t="b">
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="O17" s="23" t="b">
+      <c r="O17" s="25" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" s="24" customFormat="1" spans="1:15">
-      <c r="A18" s="30" t="s">
+    <row r="18" s="26" customFormat="1" spans="1:15">
+      <c r="A18" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="I18" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="J18" s="24" t="s">
+      <c r="J18" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="K18" s="44" t="s">
+      <c r="K18" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="24" t="b">
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
+      <c r="N18" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="O18" s="24" t="b">
+      <c r="O18" s="26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19" s="24" customFormat="1" spans="1:18">
-      <c r="A19" s="30" t="s">
+    <row r="19" s="26" customFormat="1" spans="1:18">
+      <c r="A19" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="H19" s="24" t="s">
+      <c r="H19" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="I19" s="24" t="s">
+      <c r="I19" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="J19" s="24" t="s">
+      <c r="J19" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="K19" s="44" t="s">
+      <c r="K19" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
-      <c r="O19" s="24" t="b">
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="O19" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="R19" s="24" t="b">
+      <c r="R19" s="26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20" s="24" customFormat="1" spans="1:18">
-      <c r="A20" s="30" t="s">
+    <row r="20" s="26" customFormat="1" spans="1:18">
+      <c r="A20" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="24" t="s">
+      <c r="H20" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="I20" s="24" t="s">
+      <c r="I20" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="K20" s="44" t="s">
+      <c r="K20" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="L20" s="45"/>
-      <c r="M20" s="45"/>
-      <c r="O20" s="24" t="b">
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
+      <c r="O20" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="R20" s="24" t="b">
+      <c r="R20" s="26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21" s="24" customFormat="1" spans="1:18">
-      <c r="A21" s="30" t="s">
+    <row r="21" s="26" customFormat="1" spans="1:18">
+      <c r="A21" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="I21" s="24" t="s">
+      <c r="I21" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="J21" s="24" t="s">
+      <c r="J21" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="K21" s="44" t="s">
+      <c r="K21" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="O21" s="24" t="b">
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="O21" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="R21" s="24" t="b">
+      <c r="R21" s="26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22" s="25" customFormat="1" spans="1:15">
-      <c r="A22" s="31" t="s">
+    <row r="22" s="27" customFormat="1" spans="1:15">
+      <c r="A22" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="25" t="s">
+      <c r="H22" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="I22" s="25" t="s">
+      <c r="I22" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="J22" s="25" t="s">
+      <c r="J22" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="L22" s="47"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="25" t="b">
+      <c r="L22" s="49"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="O22" s="25" t="b">
+      <c r="O22" s="27" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37"/>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1"/>
@@ -2836,7 +2849,7 @@
       <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -2859,10 +2872,10 @@
       <c r="D2" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="17" t="s">
         <v>143</v>
       </c>
       <c r="G2" s="1"/>
@@ -2880,10 +2893,10 @@
       <c r="D3" t="s">
         <v>146</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="17" t="s">
         <v>148</v>
       </c>
       <c r="G3" s="1"/>
@@ -2901,10 +2914,10 @@
       <c r="D4" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="19" t="s">
         <v>154</v>
       </c>
       <c r="G4" s="4"/>
@@ -2922,10 +2935,10 @@
       <c r="D5" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="19" t="s">
         <v>159</v>
       </c>
       <c r="G5" s="4"/>
@@ -2943,13 +2956,13 @@
       <c r="D6" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="21" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2966,10 +2979,10 @@
       <c r="D7" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="17" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2986,10 +2999,10 @@
       <c r="D8" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="17" t="s">
         <v>174</v>
       </c>
     </row>
@@ -3006,10 +3019,10 @@
       <c r="D9" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="17" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3026,10 +3039,10 @@
       <c r="D10" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="17" t="s">
         <v>184</v>
       </c>
     </row>
@@ -3046,10 +3059,10 @@
       <c r="D11" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="17" t="s">
         <v>189</v>
       </c>
     </row>
@@ -3066,10 +3079,10 @@
       <c r="D12" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="17" t="s">
         <v>194</v>
       </c>
     </row>
@@ -3086,10 +3099,10 @@
       <c r="D13" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="17" t="s">
         <v>199</v>
       </c>
     </row>
@@ -3106,10 +3119,10 @@
       <c r="D14" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="17" t="s">
         <v>204</v>
       </c>
     </row>
@@ -3126,10 +3139,10 @@
       <c r="D15" t="s">
         <v>207</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="17" t="s">
         <v>209</v>
       </c>
     </row>
@@ -3146,10 +3159,10 @@
       <c r="D16" t="s">
         <v>212</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="17" t="s">
         <v>214</v>
       </c>
     </row>
@@ -3166,10 +3179,10 @@
       <c r="D17" t="s">
         <v>217</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="17" t="s">
         <v>219</v>
       </c>
     </row>
@@ -3186,10 +3199,10 @@
       <c r="D18" t="s">
         <v>222</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="17" t="s">
         <v>224</v>
       </c>
     </row>
@@ -3206,10 +3219,10 @@
       <c r="D19" t="s">
         <v>227</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="17" t="s">
         <v>229</v>
       </c>
     </row>
@@ -3226,10 +3239,10 @@
       <c r="D20" t="s">
         <v>232</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="17" t="s">
         <v>234</v>
       </c>
     </row>
@@ -3246,10 +3259,10 @@
       <c r="D21" t="s">
         <v>237</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="17" t="s">
         <v>239</v>
       </c>
     </row>
@@ -3266,10 +3279,10 @@
       <c r="D22" t="s">
         <v>242</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="17" t="s">
         <v>244</v>
       </c>
     </row>
@@ -3286,10 +3299,10 @@
       <c r="D23" t="s">
         <v>247</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="17" t="s">
         <v>249</v>
       </c>
     </row>
@@ -3306,10 +3319,10 @@
       <c r="D24" t="s">
         <v>252</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="F24" s="23" t="s">
         <v>254</v>
       </c>
       <c r="G24" s="11"/>
@@ -3327,35 +3340,59 @@
       <c r="D25" t="s">
         <v>202</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="F25" s="23" t="s">
         <v>204</v>
       </c>
       <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="9"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
+      <c r="A26" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>256</v>
+      </c>
       <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="9"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
+      <c r="A27" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>256</v>
+      </c>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="9"/>
-      <c r="B28" s="12"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
@@ -3364,7 +3401,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="9"/>
-      <c r="B29" s="12"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
@@ -3373,7 +3410,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="9"/>
-      <c r="B30" s="12"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
@@ -3382,7 +3419,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="9"/>
-      <c r="B31" s="12"/>
+      <c r="B31" s="14"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
@@ -3391,7 +3428,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="9"/>
-      <c r="B32" s="12"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
@@ -3400,7 +3437,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="9"/>
-      <c r="B33" s="12"/>
+      <c r="B33" s="14"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
@@ -3409,7 +3446,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="9"/>
-      <c r="B34" s="12"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -3418,7 +3455,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="9"/>
-      <c r="B35" s="12"/>
+      <c r="B35" s="14"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
@@ -3427,7 +3464,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="9"/>
-      <c r="B36" s="12"/>
+      <c r="B36" s="14"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -3436,7 +3473,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="9"/>
-      <c r="B37" s="12"/>
+      <c r="B37" s="14"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -3501,27 +3538,27 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C2" t="s">
         <v>207</v>
@@ -3530,7 +3567,7 @@
         <v>208</v>
       </c>
       <c r="E2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
